--- a/usecase2_demand_forecasting/final_output/final_output_forecast_staffing.xlsx
+++ b/usecase2_demand_forecasting/final_output/final_output_forecast_staffing.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast_Staffing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,15 +31,27 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="12"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001B2A4A"/>
+      <sz val="13"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B2A4A"/>
+        <bgColor rgb="001B2A4A"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,11 +66,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -148,142 +163,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Required vs Available FTE (weekly avg)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Summary'!C8</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Summary'!$A$9:$A$15</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Summary'!$C$9:$C$15</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Summary'!D8</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Summary'!$A$9:$A$15</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Summary'!$D$9:$D$15</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>FTE</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Staffing Gap (weekly avg FTE, positive = short-staffed)</a:t>
+              <a:t>Model Accuracy Comparison (Holdout MAPE %)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -298,7 +178,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Summary'!E8</f>
+              <f>'Analysis'!B2</f>
             </strRef>
           </tx>
           <spPr>
@@ -308,15 +188,18 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Summary'!$A$9:$A$15</f>
+              <f>'Analysis'!$A$3:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Summary'!$E$9:$E$15</f>
+              <f>'Analysis'!$B$3:$B$4</f>
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -348,7 +231,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Gap (FTE)</a:t>
+                  <a:t>Holdout MAPE %</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -359,16 +242,13 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -380,7 +260,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Monthly Forecast Volume vs Required FTE</a:t>
+              <a:t>Weekly Rollup - Volume vs Staffing Gap</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -395,7 +275,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Summary'!B19</f>
+              <f>'Analysis'!B16</f>
             </strRef>
           </tx>
           <spPr>
@@ -405,15 +285,18 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Summary'!$A$20:$A$22</f>
+              <f>'Analysis'!$A$17:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Summary'!$B$20:$B$22</f>
+              <f>'Analysis'!$B$17:$B$23</f>
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -425,7 +308,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Summary'!C19</f>
+              <f>'Analysis'!E16</f>
             </strRef>
           </tx>
           <spPr>
@@ -443,10 +326,13 @@
           </marker>
           <val>
             <numRef>
-              <f>'Summary'!$C$20:$C$22</f>
+              <f>'Analysis'!$E$17:$E$23</f>
             </numRef>
           </val>
         </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
         <axId val="10"/>
         <axId val="200"/>
       </lineChart>
@@ -504,7 +390,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Required FTE</a:t>
+                  <a:t>Staffing Gap (FTE)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -517,7 +403,170 @@
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Monthly Rollup - Volume vs Staffing Gap</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Analysis'!B30</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Analysis'!$A$31:$A$33</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Analysis'!$B$31:$B$33</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Analysis'!E30</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'Analysis'!$E$31:$E$33</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <axId val="10"/>
+        <axId val="200"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Forecast Volume</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <crosses val="autoZero"/>
+      </valAx>
+      <valAx>
+        <axId val="200"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Staffing Gap (FTE)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <crosses val="max"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -529,12 +578,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>2</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="3960000" cy="2340000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -551,12 +600,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>5</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="3960000" cy="2340000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -573,12 +622,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>5</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="3960000" cy="2340000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -887,36 +936,43 @@
   </sheetPr>
   <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>forecast_volume</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>required_fte</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>available_fte</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>staffing_gap_fte</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>46322</v>
       </c>
       <c r="B2" t="n">
@@ -933,7 +989,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>46323</v>
       </c>
       <c r="B3" t="n">
@@ -950,7 +1006,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>46324</v>
       </c>
       <c r="B4" t="n">
@@ -967,7 +1023,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>46325</v>
       </c>
       <c r="B5" t="n">
@@ -984,7 +1040,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>46326</v>
       </c>
       <c r="B6" t="n">
@@ -1001,7 +1057,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>46327</v>
       </c>
       <c r="B7" t="n">
@@ -1018,7 +1074,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>46328</v>
       </c>
       <c r="B8" t="n">
@@ -1035,7 +1091,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>46329</v>
       </c>
       <c r="B9" t="n">
@@ -1052,7 +1108,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>46330</v>
       </c>
       <c r="B10" t="n">
@@ -1069,7 +1125,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>46331</v>
       </c>
       <c r="B11" t="n">
@@ -1086,7 +1142,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>46332</v>
       </c>
       <c r="B12" t="n">
@@ -1103,7 +1159,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>46333</v>
       </c>
       <c r="B13" t="n">
@@ -1120,7 +1176,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>46334</v>
       </c>
       <c r="B14" t="n">
@@ -1137,7 +1193,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>46335</v>
       </c>
       <c r="B15" t="n">
@@ -1154,7 +1210,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>46336</v>
       </c>
       <c r="B16" t="n">
@@ -1171,7 +1227,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>46337</v>
       </c>
       <c r="B17" t="n">
@@ -1188,7 +1244,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>46338</v>
       </c>
       <c r="B18" t="n">
@@ -1205,7 +1261,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>46339</v>
       </c>
       <c r="B19" t="n">
@@ -1222,7 +1278,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>46340</v>
       </c>
       <c r="B20" t="n">
@@ -1239,7 +1295,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>46341</v>
       </c>
       <c r="B21" t="n">
@@ -1256,7 +1312,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>46342</v>
       </c>
       <c r="B22" t="n">
@@ -1273,7 +1329,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>46343</v>
       </c>
       <c r="B23" t="n">
@@ -1290,7 +1346,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>46344</v>
       </c>
       <c r="B24" t="n">
@@ -1307,7 +1363,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>46345</v>
       </c>
       <c r="B25" t="n">
@@ -1324,7 +1380,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>46346</v>
       </c>
       <c r="B26" t="n">
@@ -1341,7 +1397,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>46347</v>
       </c>
       <c r="B27" t="n">
@@ -1358,7 +1414,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>46348</v>
       </c>
       <c r="B28" t="n">
@@ -1375,7 +1431,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>46349</v>
       </c>
       <c r="B29" t="n">
@@ -1392,7 +1448,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>46350</v>
       </c>
       <c r="B30" t="n">
@@ -1409,7 +1465,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>46351</v>
       </c>
       <c r="B31" t="n">
@@ -1426,7 +1482,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>46352</v>
       </c>
       <c r="B32" t="n">
@@ -1443,7 +1499,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>46353</v>
       </c>
       <c r="B33" t="n">
@@ -1460,7 +1516,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>46354</v>
       </c>
       <c r="B34" t="n">
@@ -1477,7 +1533,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>46355</v>
       </c>
       <c r="B35" t="n">
@@ -1494,7 +1550,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>46356</v>
       </c>
       <c r="B36" t="n">
@@ -1511,7 +1567,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>46357</v>
       </c>
       <c r="B37" t="n">
@@ -1528,7 +1584,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>46358</v>
       </c>
       <c r="B38" t="n">
@@ -1545,7 +1601,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>46359</v>
       </c>
       <c r="B39" t="n">
@@ -1562,7 +1618,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>46360</v>
       </c>
       <c r="B40" t="n">
@@ -1579,7 +1635,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>46361</v>
       </c>
       <c r="B41" t="n">
@@ -1596,7 +1652,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>46362</v>
       </c>
       <c r="B42" t="n">
@@ -1613,7 +1669,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>46363</v>
       </c>
       <c r="B43" t="n">
@@ -1640,23 +1696,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Model Accuracy Comparison</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Model Accuracy Comparison (Holdout MAPE %)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>holdout_mape_pct</t>
         </is>
@@ -1682,233 +1745,131 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Weekly Rollup</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Weekly Rollup - Volume vs Staffing Gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>period</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>forecast_volume</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>required_fte</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>available_fte</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>staffing_gap_fte</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
+    <row r="17">
+      <c r="A17" s="3" t="n">
         <v>46321</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B17" t="n">
         <v>1811.7</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C17" t="n">
         <v>27.6</v>
       </c>
-      <c r="D9" t="n">
-        <v>25</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E17" t="n">
         <v>2.6</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
+    <row r="18">
+      <c r="A18" s="3" t="n">
         <v>46328</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B18" t="n">
         <v>1805.6</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C18" t="n">
         <v>27.5</v>
       </c>
-      <c r="D10" t="n">
-        <v>25</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="D18" t="n">
+        <v>25</v>
+      </c>
+      <c r="E18" t="n">
         <v>2.5</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
+    <row r="19">
+      <c r="A19" s="3" t="n">
         <v>46335</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B19" t="n">
         <v>1806.6</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C19" t="n">
         <v>27.5</v>
       </c>
-      <c r="D11" t="n">
-        <v>25</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="D19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" t="n">
         <v>2.5</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
+    <row r="20">
+      <c r="A20" s="3" t="n">
         <v>46342</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B20" t="n">
         <v>1807.6</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C20" t="n">
         <v>27.5</v>
       </c>
-      <c r="D12" t="n">
-        <v>25</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="D20" t="n">
+        <v>25</v>
+      </c>
+      <c r="E20" t="n">
         <v>2.5</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
+    <row r="21">
+      <c r="A21" s="3" t="n">
         <v>46349</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B21" t="n">
         <v>1808.6</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C21" t="n">
         <v>27.5</v>
       </c>
-      <c r="D13" t="n">
-        <v>25</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="D21" t="n">
+        <v>25</v>
+      </c>
+      <c r="E21" t="n">
         <v>2.5</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
+    <row r="22">
+      <c r="A22" s="3" t="n">
         <v>46356</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B22" t="n">
         <v>1809.6</v>
-      </c>
-      <c r="C14" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="D14" t="n">
-        <v>25</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>46363</v>
-      </c>
-      <c r="B15" t="n">
-        <v>1768</v>
-      </c>
-      <c r="C15" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="D15" t="n">
-        <v>25</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Monthly Rollup</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>period</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>forecast_volume</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>required_fte</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>available_fte</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>staffing_gap_fte</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B20" t="n">
-        <v>1862</v>
-      </c>
-      <c r="C20" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="D20" t="n">
-        <v>25</v>
-      </c>
-      <c r="E20" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>46327</v>
-      </c>
-      <c r="B21" t="n">
-        <v>1797.5</v>
-      </c>
-      <c r="C21" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="D21" t="n">
-        <v>25</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>46357</v>
-      </c>
-      <c r="B22" t="n">
-        <v>1809.7</v>
       </c>
       <c r="C22" t="n">
         <v>27.6</v>
@@ -1920,20 +1881,109 @@
         <v>2.6</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>46363</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1768</v>
+      </c>
+      <c r="C23" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="D23" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Monthly Rollup - Volume vs Staffing Gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>period</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>forecast_volume</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>required_fte</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>available_fte</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>staffing_gap_fte</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C31" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>25</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1797.5</v>
+      </c>
+      <c r="C32" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>25</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1809.7</v>
+      </c>
+      <c r="C33" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="D33" t="n">
+        <v>25</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/usecase2_demand_forecasting/final_output/final_output_forecast_staffing.xlsx
+++ b/usecase2_demand_forecasting/final_output/final_output_forecast_staffing.xlsx
@@ -209,9 +209,11 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -221,7 +223,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -275,7 +276,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Analysis'!B16</f>
+              <f>'Analysis'!B19</f>
             </strRef>
           </tx>
           <spPr>
@@ -285,12 +286,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Analysis'!$A$17:$A$23</f>
+              <f>'Analysis'!$A$20:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Analysis'!$B$17:$B$23</f>
+              <f>'Analysis'!$B$20:$B$26</f>
             </numRef>
           </val>
         </ser>
@@ -308,7 +309,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Analysis'!E16</f>
+              <f>'Analysis'!E19</f>
             </strRef>
           </tx>
           <spPr>
@@ -326,7 +327,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Analysis'!$E$17:$E$23</f>
+              <f>'Analysis'!$E$20:$E$26</f>
             </numRef>
           </val>
         </ser>
@@ -341,9 +342,11 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -353,7 +356,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -380,7 +382,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -438,7 +439,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Analysis'!B30</f>
+              <f>'Analysis'!B36</f>
             </strRef>
           </tx>
           <spPr>
@@ -448,12 +449,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Analysis'!$A$31:$A$33</f>
+              <f>'Analysis'!$A$37:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Analysis'!$B$31:$B$33</f>
+              <f>'Analysis'!$B$37:$B$39</f>
             </numRef>
           </val>
         </ser>
@@ -471,7 +472,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Analysis'!E30</f>
+              <f>'Analysis'!E36</f>
             </strRef>
           </tx>
           <spPr>
@@ -489,7 +490,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Analysis'!$E$31:$E$33</f>
+              <f>'Analysis'!$E$37:$E$39</f>
             </numRef>
           </val>
         </ser>
@@ -504,9 +505,11 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -516,7 +519,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -543,7 +545,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -583,7 +584,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3960000" cy="2340000"/>
+    <ext cx="8640000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -602,10 +603,10 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3960000" cy="2340000"/>
+    <ext cx="8640000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -624,10 +625,10 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3960000" cy="2340000"/>
+    <ext cx="8640000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -1696,7 +1697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1745,114 +1746,63 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Weekly Rollup - Volume vs Staffing Gap</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>period</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>forecast_volume</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>required_fte</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>available_fte</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>staffing_gap_fte</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>46321</v>
-      </c>
-      <c r="B17" t="n">
-        <v>1811.7</v>
-      </c>
-      <c r="C17" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="D17" t="n">
-        <v>25</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>46328</v>
-      </c>
-      <c r="B18" t="n">
-        <v>1805.6</v>
-      </c>
-      <c r="C18" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="D18" t="n">
-        <v>25</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>46335</v>
-      </c>
-      <c r="B19" t="n">
-        <v>1806.6</v>
-      </c>
-      <c r="C19" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="D19" t="n">
-        <v>25</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46342</v>
+        <v>46321</v>
       </c>
       <c r="B20" t="n">
-        <v>1807.6</v>
+        <v>1811.7</v>
       </c>
       <c r="C20" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="D20" t="n">
         <v>25</v>
       </c>
       <c r="E20" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46349</v>
+        <v>46328</v>
       </c>
       <c r="B21" t="n">
-        <v>1808.6</v>
+        <v>1805.6</v>
       </c>
       <c r="C21" t="n">
         <v>27.5</v>
@@ -1866,120 +1816,171 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46356</v>
+        <v>46335</v>
       </c>
       <c r="B22" t="n">
-        <v>1809.6</v>
+        <v>1806.6</v>
       </c>
       <c r="C22" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="D22" t="n">
         <v>25</v>
       </c>
       <c r="E22" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
+        <v>46342</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1807.6</v>
+      </c>
+      <c r="C23" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>46349</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1808.6</v>
+      </c>
+      <c r="C24" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>25</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>46356</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1809.6</v>
+      </c>
+      <c r="C25" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="D25" t="n">
+        <v>25</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
         <v>46363</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B26" t="n">
         <v>1768</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C26" t="n">
         <v>26.9</v>
       </c>
-      <c r="D23" t="n">
-        <v>25</v>
-      </c>
-      <c r="E23" t="n">
+      <c r="D26" t="n">
+        <v>25</v>
+      </c>
+      <c r="E26" t="n">
         <v>1.9</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Monthly Rollup - Volume vs Staffing Gap</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>period</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>forecast_volume</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>required_fte</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>available_fte</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>staffing_gap_fte</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
+    <row r="37">
+      <c r="A37" s="3" t="n">
         <v>46296</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B37" t="n">
         <v>1862</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C37" t="n">
         <v>28.3</v>
       </c>
-      <c r="D31" t="n">
-        <v>25</v>
-      </c>
-      <c r="E31" t="n">
+      <c r="D37" t="n">
+        <v>25</v>
+      </c>
+      <c r="E37" t="n">
         <v>3.3</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
+    <row r="38">
+      <c r="A38" s="3" t="n">
         <v>46327</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B38" t="n">
         <v>1797.5</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C38" t="n">
         <v>27.4</v>
       </c>
-      <c r="D32" t="n">
-        <v>25</v>
-      </c>
-      <c r="E32" t="n">
+      <c r="D38" t="n">
+        <v>25</v>
+      </c>
+      <c r="E38" t="n">
         <v>2.4</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
+    <row r="39">
+      <c r="A39" s="3" t="n">
         <v>46357</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B39" t="n">
         <v>1809.7</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C39" t="n">
         <v>27.6</v>
       </c>
-      <c r="D33" t="n">
-        <v>25</v>
-      </c>
-      <c r="E33" t="n">
+      <c r="D39" t="n">
+        <v>25</v>
+      </c>
+      <c r="E39" t="n">
         <v>2.6</v>
       </c>
     </row>

--- a/usecase2_demand_forecasting/final_output/final_output_forecast_staffing.xlsx
+++ b/usecase2_demand_forecasting/final_output/final_output_forecast_staffing.xlsx
@@ -198,7 +198,12 @@
           </val>
         </ser>
         <dLbls>
+          <showLegendKey val="0"/>
           <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
         </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
@@ -296,7 +301,12 @@
           </val>
         </ser>
         <dLbls>
+          <showLegendKey val="0"/>
           <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
         </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
@@ -332,7 +342,12 @@
           </val>
         </ser>
         <dLbls>
+          <showLegendKey val="0"/>
           <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
         </dLbls>
         <axId val="10"/>
         <axId val="200"/>
@@ -459,7 +474,12 @@
           </val>
         </ser>
         <dLbls>
+          <showLegendKey val="0"/>
           <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
         </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
@@ -495,7 +515,12 @@
           </val>
         </ser>
         <dLbls>
+          <showLegendKey val="0"/>
           <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
         </dLbls>
         <axId val="10"/>
         <axId val="200"/>

--- a/usecase2_demand_forecasting/final_output/final_output_forecast_staffing.xlsx
+++ b/usecase2_demand_forecasting/final_output/final_output_forecast_staffing.xlsx
@@ -1002,16 +1002,16 @@
         <v>46322</v>
       </c>
       <c r="B2" t="n">
-        <v>1864</v>
+        <v>1716</v>
       </c>
       <c r="C2" t="n">
-        <v>28.4</v>
+        <v>25.8</v>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="3">
@@ -1019,16 +1019,16 @@
         <v>46323</v>
       </c>
       <c r="B3" t="n">
-        <v>1880</v>
+        <v>1743</v>
       </c>
       <c r="C3" t="n">
-        <v>28.6</v>
+        <v>26.2</v>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="4">
@@ -1036,16 +1036,16 @@
         <v>46324</v>
       </c>
       <c r="B4" t="n">
-        <v>1872</v>
+        <v>1787</v>
       </c>
       <c r="C4" t="n">
-        <v>28.5</v>
+        <v>26.8</v>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="5">
@@ -1053,16 +1053,16 @@
         <v>46325</v>
       </c>
       <c r="B5" t="n">
-        <v>1821</v>
+        <v>1738</v>
       </c>
       <c r="C5" t="n">
-        <v>27.7</v>
+        <v>26.1</v>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="6">
@@ -1070,16 +1070,16 @@
         <v>46326</v>
       </c>
       <c r="B6" t="n">
-        <v>1873</v>
+        <v>1710</v>
       </c>
       <c r="C6" t="n">
-        <v>28.5</v>
+        <v>25.7</v>
       </c>
       <c r="D6" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="7">
@@ -1087,16 +1087,16 @@
         <v>46327</v>
       </c>
       <c r="B7" t="n">
-        <v>1560</v>
+        <v>1447</v>
       </c>
       <c r="C7" t="n">
-        <v>23.7</v>
+        <v>21.7</v>
       </c>
       <c r="D7" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="8">
@@ -1104,16 +1104,16 @@
         <v>46328</v>
       </c>
       <c r="B8" t="n">
-        <v>1763</v>
+        <v>1742</v>
       </c>
       <c r="C8" t="n">
-        <v>26.8</v>
+        <v>26.1</v>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="9">
@@ -1121,16 +1121,16 @@
         <v>46329</v>
       </c>
       <c r="B9" t="n">
-        <v>1865</v>
+        <v>1716</v>
       </c>
       <c r="C9" t="n">
-        <v>28.4</v>
+        <v>25.8</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="10">
@@ -1138,16 +1138,16 @@
         <v>46330</v>
       </c>
       <c r="B10" t="n">
-        <v>1881</v>
+        <v>1743</v>
       </c>
       <c r="C10" t="n">
-        <v>28.6</v>
+        <v>26.2</v>
       </c>
       <c r="D10" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="11">
@@ -1155,16 +1155,16 @@
         <v>46331</v>
       </c>
       <c r="B11" t="n">
-        <v>1873</v>
+        <v>1787</v>
       </c>
       <c r="C11" t="n">
-        <v>28.5</v>
+        <v>26.8</v>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="12">
@@ -1172,16 +1172,16 @@
         <v>46332</v>
       </c>
       <c r="B12" t="n">
-        <v>1822</v>
+        <v>1738</v>
       </c>
       <c r="C12" t="n">
-        <v>27.7</v>
+        <v>26.1</v>
       </c>
       <c r="D12" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="13">
@@ -1189,16 +1189,16 @@
         <v>46333</v>
       </c>
       <c r="B13" t="n">
-        <v>1874</v>
+        <v>1710</v>
       </c>
       <c r="C13" t="n">
-        <v>28.5</v>
+        <v>25.7</v>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="14">
@@ -1206,16 +1206,16 @@
         <v>46334</v>
       </c>
       <c r="B14" t="n">
-        <v>1561</v>
+        <v>1447</v>
       </c>
       <c r="C14" t="n">
-        <v>23.8</v>
+        <v>21.7</v>
       </c>
       <c r="D14" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.2</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="15">
@@ -1223,16 +1223,16 @@
         <v>46335</v>
       </c>
       <c r="B15" t="n">
-        <v>1764</v>
+        <v>1742</v>
       </c>
       <c r="C15" t="n">
-        <v>26.8</v>
+        <v>26.1</v>
       </c>
       <c r="D15" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="16">
@@ -1240,16 +1240,16 @@
         <v>46336</v>
       </c>
       <c r="B16" t="n">
-        <v>1866</v>
+        <v>1716</v>
       </c>
       <c r="C16" t="n">
-        <v>28.4</v>
+        <v>25.8</v>
       </c>
       <c r="D16" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="17">
@@ -1257,16 +1257,16 @@
         <v>46337</v>
       </c>
       <c r="B17" t="n">
-        <v>1882</v>
+        <v>1743</v>
       </c>
       <c r="C17" t="n">
-        <v>28.6</v>
+        <v>26.2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E17" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="18">
@@ -1274,16 +1274,16 @@
         <v>46338</v>
       </c>
       <c r="B18" t="n">
-        <v>1874</v>
+        <v>1787</v>
       </c>
       <c r="C18" t="n">
-        <v>28.5</v>
+        <v>26.8</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E18" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="19">
@@ -1291,16 +1291,16 @@
         <v>46339</v>
       </c>
       <c r="B19" t="n">
-        <v>1823</v>
+        <v>1738</v>
       </c>
       <c r="C19" t="n">
-        <v>27.7</v>
+        <v>26.1</v>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="20">
@@ -1308,16 +1308,16 @@
         <v>46340</v>
       </c>
       <c r="B20" t="n">
-        <v>1875</v>
+        <v>1710</v>
       </c>
       <c r="C20" t="n">
-        <v>28.5</v>
+        <v>25.7</v>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E20" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="21">
@@ -1325,16 +1325,16 @@
         <v>46341</v>
       </c>
       <c r="B21" t="n">
-        <v>1562</v>
+        <v>1447</v>
       </c>
       <c r="C21" t="n">
-        <v>23.8</v>
+        <v>21.7</v>
       </c>
       <c r="D21" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="22">
@@ -1342,16 +1342,16 @@
         <v>46342</v>
       </c>
       <c r="B22" t="n">
-        <v>1765</v>
+        <v>1742</v>
       </c>
       <c r="C22" t="n">
-        <v>26.9</v>
+        <v>26.1</v>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E22" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="23">
@@ -1359,16 +1359,16 @@
         <v>46343</v>
       </c>
       <c r="B23" t="n">
-        <v>1867</v>
+        <v>1716</v>
       </c>
       <c r="C23" t="n">
-        <v>28.4</v>
+        <v>25.8</v>
       </c>
       <c r="D23" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E23" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="24">
@@ -1376,16 +1376,16 @@
         <v>46344</v>
       </c>
       <c r="B24" t="n">
-        <v>1883</v>
+        <v>1743</v>
       </c>
       <c r="C24" t="n">
-        <v>28.7</v>
+        <v>26.2</v>
       </c>
       <c r="D24" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E24" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="25">
@@ -1393,16 +1393,16 @@
         <v>46345</v>
       </c>
       <c r="B25" t="n">
-        <v>1875</v>
+        <v>1787</v>
       </c>
       <c r="C25" t="n">
-        <v>28.6</v>
+        <v>26.8</v>
       </c>
       <c r="D25" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E25" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="26">
@@ -1410,16 +1410,16 @@
         <v>46346</v>
       </c>
       <c r="B26" t="n">
-        <v>1824</v>
+        <v>1738</v>
       </c>
       <c r="C26" t="n">
-        <v>27.8</v>
+        <v>26.1</v>
       </c>
       <c r="D26" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E26" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="27">
@@ -1427,16 +1427,16 @@
         <v>46347</v>
       </c>
       <c r="B27" t="n">
-        <v>1876</v>
+        <v>1710</v>
       </c>
       <c r="C27" t="n">
-        <v>28.6</v>
+        <v>25.7</v>
       </c>
       <c r="D27" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E27" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="28">
@@ -1444,16 +1444,16 @@
         <v>46348</v>
       </c>
       <c r="B28" t="n">
-        <v>1563</v>
+        <v>1447</v>
       </c>
       <c r="C28" t="n">
-        <v>23.8</v>
+        <v>21.7</v>
       </c>
       <c r="D28" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.2</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="29">
@@ -1461,16 +1461,16 @@
         <v>46349</v>
       </c>
       <c r="B29" t="n">
-        <v>1766</v>
+        <v>1742</v>
       </c>
       <c r="C29" t="n">
-        <v>26.9</v>
+        <v>26.1</v>
       </c>
       <c r="D29" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E29" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="30">
@@ -1478,16 +1478,16 @@
         <v>46350</v>
       </c>
       <c r="B30" t="n">
-        <v>1868</v>
+        <v>1716</v>
       </c>
       <c r="C30" t="n">
-        <v>28.4</v>
+        <v>25.8</v>
       </c>
       <c r="D30" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E30" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="31">
@@ -1495,16 +1495,16 @@
         <v>46351</v>
       </c>
       <c r="B31" t="n">
-        <v>1884</v>
+        <v>1743</v>
       </c>
       <c r="C31" t="n">
-        <v>28.7</v>
+        <v>26.2</v>
       </c>
       <c r="D31" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E31" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="32">
@@ -1512,16 +1512,16 @@
         <v>46352</v>
       </c>
       <c r="B32" t="n">
-        <v>1876</v>
+        <v>1787</v>
       </c>
       <c r="C32" t="n">
-        <v>28.6</v>
+        <v>26.8</v>
       </c>
       <c r="D32" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E32" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="33">
@@ -1529,16 +1529,16 @@
         <v>46353</v>
       </c>
       <c r="B33" t="n">
-        <v>1825</v>
+        <v>1738</v>
       </c>
       <c r="C33" t="n">
-        <v>27.8</v>
+        <v>26.1</v>
       </c>
       <c r="D33" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E33" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="34">
@@ -1546,16 +1546,16 @@
         <v>46354</v>
       </c>
       <c r="B34" t="n">
-        <v>1877</v>
+        <v>1710</v>
       </c>
       <c r="C34" t="n">
-        <v>28.6</v>
+        <v>25.7</v>
       </c>
       <c r="D34" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E34" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="35">
@@ -1563,16 +1563,16 @@
         <v>46355</v>
       </c>
       <c r="B35" t="n">
-        <v>1564</v>
+        <v>1447</v>
       </c>
       <c r="C35" t="n">
-        <v>23.8</v>
+        <v>21.7</v>
       </c>
       <c r="D35" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.2</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="36">
@@ -1580,16 +1580,16 @@
         <v>46356</v>
       </c>
       <c r="B36" t="n">
-        <v>1767</v>
+        <v>1742</v>
       </c>
       <c r="C36" t="n">
-        <v>26.9</v>
+        <v>26.1</v>
       </c>
       <c r="D36" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E36" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="37">
@@ -1597,16 +1597,16 @@
         <v>46357</v>
       </c>
       <c r="B37" t="n">
-        <v>1869</v>
+        <v>1716</v>
       </c>
       <c r="C37" t="n">
-        <v>28.5</v>
+        <v>25.8</v>
       </c>
       <c r="D37" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E37" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="38">
@@ -1614,16 +1614,16 @@
         <v>46358</v>
       </c>
       <c r="B38" t="n">
-        <v>1885</v>
+        <v>1743</v>
       </c>
       <c r="C38" t="n">
-        <v>28.7</v>
+        <v>26.2</v>
       </c>
       <c r="D38" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E38" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="39">
@@ -1631,16 +1631,16 @@
         <v>46359</v>
       </c>
       <c r="B39" t="n">
-        <v>1877</v>
+        <v>1787</v>
       </c>
       <c r="C39" t="n">
-        <v>28.6</v>
+        <v>26.8</v>
       </c>
       <c r="D39" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E39" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="40">
@@ -1648,16 +1648,16 @@
         <v>46360</v>
       </c>
       <c r="B40" t="n">
-        <v>1826</v>
+        <v>1738</v>
       </c>
       <c r="C40" t="n">
-        <v>27.8</v>
+        <v>26.1</v>
       </c>
       <c r="D40" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E40" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="41">
@@ -1665,16 +1665,16 @@
         <v>46361</v>
       </c>
       <c r="B41" t="n">
-        <v>1878</v>
+        <v>1710</v>
       </c>
       <c r="C41" t="n">
-        <v>28.6</v>
+        <v>25.7</v>
       </c>
       <c r="D41" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E41" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="42">
@@ -1682,16 +1682,16 @@
         <v>46362</v>
       </c>
       <c r="B42" t="n">
-        <v>1565</v>
+        <v>1447</v>
       </c>
       <c r="C42" t="n">
-        <v>23.8</v>
+        <v>21.7</v>
       </c>
       <c r="D42" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.2</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="43">
@@ -1699,16 +1699,16 @@
         <v>46363</v>
       </c>
       <c r="B43" t="n">
-        <v>1768</v>
+        <v>1742</v>
       </c>
       <c r="C43" t="n">
-        <v>26.9</v>
+        <v>26.1</v>
       </c>
       <c r="D43" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E43" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.1</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="4">
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.8</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="18">
@@ -1810,16 +1810,16 @@
         <v>46321</v>
       </c>
       <c r="B20" t="n">
-        <v>1811.7</v>
+        <v>1690.2</v>
       </c>
       <c r="C20" t="n">
-        <v>27.6</v>
+        <v>25.4</v>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="21">
@@ -1827,16 +1827,16 @@
         <v>46328</v>
       </c>
       <c r="B21" t="n">
-        <v>1805.6</v>
+        <v>1697.6</v>
       </c>
       <c r="C21" t="n">
-        <v>27.5</v>
+        <v>25.5</v>
       </c>
       <c r="D21" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E21" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1844,16 +1844,16 @@
         <v>46335</v>
       </c>
       <c r="B22" t="n">
-        <v>1806.6</v>
+        <v>1697.6</v>
       </c>
       <c r="C22" t="n">
-        <v>27.5</v>
+        <v>25.5</v>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E22" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1861,16 +1861,16 @@
         <v>46342</v>
       </c>
       <c r="B23" t="n">
-        <v>1807.6</v>
+        <v>1697.6</v>
       </c>
       <c r="C23" t="n">
-        <v>27.5</v>
+        <v>25.5</v>
       </c>
       <c r="D23" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E23" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1878,16 +1878,16 @@
         <v>46349</v>
       </c>
       <c r="B24" t="n">
-        <v>1808.6</v>
+        <v>1697.6</v>
       </c>
       <c r="C24" t="n">
-        <v>27.5</v>
+        <v>25.5</v>
       </c>
       <c r="D24" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E24" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1895,16 +1895,16 @@
         <v>46356</v>
       </c>
       <c r="B25" t="n">
-        <v>1809.6</v>
+        <v>1697.6</v>
       </c>
       <c r="C25" t="n">
-        <v>27.6</v>
+        <v>25.5</v>
       </c>
       <c r="D25" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E25" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1912,16 +1912,16 @@
         <v>46363</v>
       </c>
       <c r="B26" t="n">
-        <v>1768</v>
+        <v>1742</v>
       </c>
       <c r="C26" t="n">
-        <v>26.9</v>
+        <v>26.1</v>
       </c>
       <c r="D26" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E26" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="35">
@@ -1963,16 +1963,16 @@
         <v>46296</v>
       </c>
       <c r="B37" t="n">
-        <v>1862</v>
+        <v>1738.8</v>
       </c>
       <c r="C37" t="n">
-        <v>28.3</v>
+        <v>26.1</v>
       </c>
       <c r="D37" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E37" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="38">
@@ -1980,16 +1980,16 @@
         <v>46327</v>
       </c>
       <c r="B38" t="n">
-        <v>1797.5</v>
+        <v>1690.7</v>
       </c>
       <c r="C38" t="n">
-        <v>27.4</v>
+        <v>25.4</v>
       </c>
       <c r="D38" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E38" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="39">
@@ -1997,16 +1997,16 @@
         <v>46357</v>
       </c>
       <c r="B39" t="n">
-        <v>1809.7</v>
+        <v>1697.6</v>
       </c>
       <c r="C39" t="n">
-        <v>27.6</v>
+        <v>25.5</v>
       </c>
       <c r="D39" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="E39" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/usecase2_demand_forecasting/final_output/final_output_forecast_staffing.xlsx
+++ b/usecase2_demand_forecasting/final_output/final_output_forecast_staffing.xlsx
@@ -281,7 +281,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Analysis'!B19</f>
+              <f>'Analysis'!B17</f>
             </strRef>
           </tx>
           <spPr>
@@ -291,12 +291,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Analysis'!$A$20:$A$26</f>
+              <f>'Analysis'!$A$18:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Analysis'!$B$20:$B$26</f>
+              <f>'Analysis'!$B$18:$B$24</f>
             </numRef>
           </val>
         </ser>
@@ -319,7 +319,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Analysis'!E19</f>
+              <f>'Analysis'!E17</f>
             </strRef>
           </tx>
           <spPr>
@@ -337,7 +337,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Analysis'!$E$20:$E$26</f>
+              <f>'Analysis'!$E$18:$E$24</f>
             </numRef>
           </val>
         </ser>
@@ -454,7 +454,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Analysis'!B36</f>
+              <f>'Analysis'!B32</f>
             </strRef>
           </tx>
           <spPr>
@@ -464,12 +464,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Analysis'!$A$37:$A$39</f>
+              <f>'Analysis'!$A$33:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Analysis'!$B$37:$B$39</f>
+              <f>'Analysis'!$B$33:$B$35</f>
             </numRef>
           </val>
         </ser>
@@ -492,7 +492,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Analysis'!E36</f>
+              <f>'Analysis'!E32</f>
             </strRef>
           </tx>
           <spPr>
@@ -510,7 +510,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Analysis'!$E$37:$E$39</f>
+              <f>'Analysis'!$E$33:$E$35</f>
             </numRef>
           </val>
         </ser>
@@ -604,12 +604,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>2</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="2880000"/>
+    <ext cx="5760000" cy="2520000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -626,12 +626,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="2880000"/>
+    <ext cx="5760000" cy="2520000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -648,12 +648,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>31</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="2880000"/>
+    <ext cx="5760000" cy="2520000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -1025,10 +1025,10 @@
         <v>26.2</v>
       </c>
       <c r="D3" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="4">
@@ -1059,10 +1059,10 @@
         <v>26.1</v>
       </c>
       <c r="D5" t="n">
-        <v>24.5</v>
+        <v>25.1</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1076,10 +1076,10 @@
         <v>25.7</v>
       </c>
       <c r="D6" t="n">
-        <v>24.5</v>
+        <v>22.7</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1093,10 +1093,10 @@
         <v>21.7</v>
       </c>
       <c r="D7" t="n">
-        <v>24.5</v>
+        <v>26.1</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="8">
@@ -1110,10 +1110,10 @@
         <v>26.1</v>
       </c>
       <c r="D8" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="9">
@@ -1127,10 +1127,10 @@
         <v>25.8</v>
       </c>
       <c r="D9" t="n">
-        <v>24.5</v>
+        <v>23.9</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="10">
@@ -1144,10 +1144,10 @@
         <v>26.2</v>
       </c>
       <c r="D10" t="n">
-        <v>24.5</v>
+        <v>23.4</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
@@ -1161,10 +1161,10 @@
         <v>26.8</v>
       </c>
       <c r="D11" t="n">
-        <v>24.5</v>
+        <v>25.4</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
@@ -1178,10 +1178,10 @@
         <v>26.1</v>
       </c>
       <c r="D12" t="n">
-        <v>24.5</v>
+        <v>25.1</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1195,10 +1195,10 @@
         <v>25.7</v>
       </c>
       <c r="D13" t="n">
-        <v>24.5</v>
+        <v>25.7</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1212,10 +1212,10 @@
         <v>21.7</v>
       </c>
       <c r="D14" t="n">
-        <v>24.5</v>
+        <v>25.3</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.8</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="15">
@@ -1229,10 +1229,10 @@
         <v>26.1</v>
       </c>
       <c r="D15" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="16">
@@ -1246,10 +1246,10 @@
         <v>25.8</v>
       </c>
       <c r="D16" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1263,10 +1263,10 @@
         <v>26.2</v>
       </c>
       <c r="D17" t="n">
-        <v>24.5</v>
+        <v>25.4</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="18">
@@ -1280,10 +1280,10 @@
         <v>26.8</v>
       </c>
       <c r="D18" t="n">
-        <v>24.5</v>
+        <v>23.6</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="19">
@@ -1297,10 +1297,10 @@
         <v>26.1</v>
       </c>
       <c r="D19" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="20">
@@ -1314,10 +1314,10 @@
         <v>25.7</v>
       </c>
       <c r="D20" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="21">
@@ -1331,10 +1331,10 @@
         <v>21.7</v>
       </c>
       <c r="D21" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="22">
@@ -1348,10 +1348,10 @@
         <v>26.1</v>
       </c>
       <c r="D22" t="n">
-        <v>24.5</v>
+        <v>25.2</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="23">
@@ -1365,10 +1365,10 @@
         <v>25.8</v>
       </c>
       <c r="D23" t="n">
-        <v>24.5</v>
+        <v>24.1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="24">
@@ -1382,10 +1382,10 @@
         <v>26.2</v>
       </c>
       <c r="D24" t="n">
-        <v>24.5</v>
+        <v>25.1</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="25">
@@ -1399,10 +1399,10 @@
         <v>26.8</v>
       </c>
       <c r="D25" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="E25" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="26">
@@ -1416,10 +1416,10 @@
         <v>26.1</v>
       </c>
       <c r="D26" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="27">
@@ -1433,10 +1433,10 @@
         <v>25.7</v>
       </c>
       <c r="D27" t="n">
-        <v>24.5</v>
+        <v>23</v>
       </c>
       <c r="E27" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="28">
@@ -1450,10 +1450,10 @@
         <v>21.7</v>
       </c>
       <c r="D28" t="n">
-        <v>24.5</v>
+        <v>23.6</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.8</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="29">
@@ -1467,10 +1467,10 @@
         <v>26.1</v>
       </c>
       <c r="D29" t="n">
-        <v>24.5</v>
+        <v>25.8</v>
       </c>
       <c r="E29" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="30">
@@ -1484,10 +1484,10 @@
         <v>25.8</v>
       </c>
       <c r="D30" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="E30" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="31">
@@ -1501,10 +1501,10 @@
         <v>26.2</v>
       </c>
       <c r="D31" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="E31" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="32">
@@ -1518,10 +1518,10 @@
         <v>26.8</v>
       </c>
       <c r="D32" t="n">
-        <v>24.5</v>
+        <v>25.4</v>
       </c>
       <c r="E32" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="33">
@@ -1535,10 +1535,10 @@
         <v>26.1</v>
       </c>
       <c r="D33" t="n">
-        <v>24.5</v>
+        <v>25.2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="34">
@@ -1552,10 +1552,10 @@
         <v>25.7</v>
       </c>
       <c r="D34" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="E34" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="35">
@@ -1569,10 +1569,10 @@
         <v>21.7</v>
       </c>
       <c r="D35" t="n">
-        <v>24.5</v>
+        <v>23.8</v>
       </c>
       <c r="E35" t="n">
-        <v>-2.8</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="36">
@@ -1586,10 +1586,10 @@
         <v>26.1</v>
       </c>
       <c r="D36" t="n">
-        <v>24.5</v>
+        <v>26.4</v>
       </c>
       <c r="E36" t="n">
-        <v>1.6</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="37">
@@ -1603,10 +1603,10 @@
         <v>25.8</v>
       </c>
       <c r="D37" t="n">
-        <v>24.5</v>
+        <v>25.1</v>
       </c>
       <c r="E37" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="38">
@@ -1620,10 +1620,10 @@
         <v>26.2</v>
       </c>
       <c r="D38" t="n">
-        <v>24.5</v>
+        <v>22.9</v>
       </c>
       <c r="E38" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="39">
@@ -1637,10 +1637,10 @@
         <v>26.8</v>
       </c>
       <c r="D39" t="n">
-        <v>24.5</v>
+        <v>25.3</v>
       </c>
       <c r="E39" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="40">
@@ -1654,10 +1654,10 @@
         <v>26.1</v>
       </c>
       <c r="D40" t="n">
-        <v>24.5</v>
+        <v>25.2</v>
       </c>
       <c r="E40" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="41">
@@ -1671,10 +1671,10 @@
         <v>25.7</v>
       </c>
       <c r="D41" t="n">
-        <v>24.5</v>
+        <v>25.3</v>
       </c>
       <c r="E41" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="42">
@@ -1688,10 +1688,10 @@
         <v>21.7</v>
       </c>
       <c r="D42" t="n">
-        <v>24.5</v>
+        <v>24.1</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.8</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="43">
@@ -1705,10 +1705,10 @@
         <v>26.1</v>
       </c>
       <c r="D43" t="n">
-        <v>24.5</v>
+        <v>25.9</v>
       </c>
       <c r="E43" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -1722,7 +1722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1771,60 +1771,94 @@
         <v>15.1</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Weekly Rollup - Volume vs Staffing Gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>period</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>forecast_volume</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>required_fte</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>available_fte</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>staffing_gap_fte</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Weekly Rollup - Volume vs Staffing Gap</t>
-        </is>
+      <c r="A18" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1690.2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>period</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>forecast_volume</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>required_fte</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>available_fte</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>staffing_gap_fte</t>
-        </is>
+      <c r="A19" s="3" t="n">
+        <v>46328</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1697.6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46321</v>
+        <v>46335</v>
       </c>
       <c r="B20" t="n">
-        <v>1690.2</v>
+        <v>1697.6</v>
       </c>
       <c r="C20" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="D20" t="n">
         <v>24.5</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46328</v>
+        <v>46342</v>
       </c>
       <c r="B21" t="n">
         <v>1697.6</v>
@@ -1833,15 +1867,15 @@
         <v>25.5</v>
       </c>
       <c r="D21" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46335</v>
+        <v>46349</v>
       </c>
       <c r="B22" t="n">
         <v>1697.6</v>
@@ -1850,15 +1884,15 @@
         <v>25.5</v>
       </c>
       <c r="D22" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46342</v>
+        <v>46356</v>
       </c>
       <c r="B23" t="n">
         <v>1697.6</v>
@@ -1867,146 +1901,112 @@
         <v>25.5</v>
       </c>
       <c r="D23" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46349</v>
+        <v>46363</v>
       </c>
       <c r="B24" t="n">
+        <v>1742</v>
+      </c>
+      <c r="C24" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Monthly Rollup - Volume vs Staffing Gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>period</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>forecast_volume</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>required_fte</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>available_fte</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>staffing_gap_fte</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1738.8</v>
+      </c>
+      <c r="C33" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1690.7</v>
+      </c>
+      <c r="C34" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="D34" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B35" t="n">
         <v>1697.6</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C35" t="n">
         <v>25.5</v>
       </c>
-      <c r="D24" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>46356</v>
-      </c>
-      <c r="B25" t="n">
-        <v>1697.6</v>
-      </c>
-      <c r="C25" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="D25" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>46363</v>
-      </c>
-      <c r="B26" t="n">
-        <v>1742</v>
-      </c>
-      <c r="C26" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>Monthly Rollup - Volume vs Staffing Gap</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>period</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>forecast_volume</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>required_fte</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>available_fte</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>staffing_gap_fte</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B37" t="n">
-        <v>1738.8</v>
-      </c>
-      <c r="C37" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="D37" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="n">
-        <v>46327</v>
-      </c>
-      <c r="B38" t="n">
-        <v>1690.7</v>
-      </c>
-      <c r="C38" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="D38" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>46357</v>
-      </c>
-      <c r="B39" t="n">
-        <v>1697.6</v>
-      </c>
-      <c r="C39" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="D39" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1</v>
+      <c r="D35" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
